--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/fiama.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/fiama.xlsx
@@ -352,7 +352,7 @@
   <si>
     <t xml:space="preserve">Dreaming Children...poor children of Elea who can never grow up.
 Those who have developed the disease lose themselves between dreams and reality, and eventually fall into a sleep from which they will never awaken. Their faces are always vacant and their hearts are elusive as if detached from outside world.
-The ether dreams the Dreaming Children weave are embodied in reality as an outburst of power or an unforeseen calamity. I've heard a whole town vanished without a trace just because some idiot startled a Dreaming Child  in jest.</t>
+The ether dreams the Dreaming Children weave are embodied in reality as an outburst of power or an unforeseen calamity. I've heard a whole town vanished without a trace just because some idiot startled a Dreaming Child in jest.</t>
   </si>
   <si>
     <t xml:space="preserve">夢見の病と呼ばれるこの不治の病を治すすべは見つかっていない。いかなる社会においても危険な存在である彼らは、古き森へとただ一人送られ、その短い命を終える。
